--- a/examples/sample_suppliers.xlsx
+++ b/examples/sample_suppliers.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -487,13 +487,11 @@
           <t>10816 1779 RT0001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>PST-1000-7572</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -501,7 +499,6 @@
           <t>Amazon.com.ca ULC</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>ON</t>
@@ -512,9 +509,6 @@
           <t>857305932RT0001</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -532,14 +526,11 @@
           <t>QC</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>1019288451 TQ 0004</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -552,15 +543,11 @@
           <t>Airalo</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>751950577RT9999</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -568,7 +555,6 @@
           <t>Typo Supplies Inc</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>ON</t>
@@ -579,9 +565,6 @@
           <t>123456789RT0001</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -589,7 +572,6 @@
           <t>Wrong Name Co</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>ON</t>
@@ -600,9 +582,6 @@
           <t>857305932RT0001</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -610,20 +589,16 @@
           <t>Bad QST Ltee</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>QC</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>1234567890TQ0001</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -631,7 +606,6 @@
           <t>UBC wrong PST</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>BC</t>
@@ -642,13 +616,11 @@
           <t>108161779RT0001</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>PST-1000-7573</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -656,37 +628,50 @@
           <t>Prairie Example Ltd</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>1234567</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Winnipeg Example Ltd</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Amazon.com.ca ULC</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>857305932RT0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NA Tutors</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>774075766RT0001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
